--- a/ResourcesPK/productPriceApproval.xlsx
+++ b/ResourcesPK/productPriceApproval.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
   <si>
     <t>Code*</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>QQ</t>
+  </si>
+  <si>
+    <t>366.00</t>
   </si>
 </sst>
 </file>
@@ -113,7 +116,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -147,7 +150,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -441,7 +444,7 @@
     <col min="7" max="7" width="19.1796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.26953125" customWidth="1"/>
     <col min="11" max="11" width="10.90625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
@@ -539,8 +542,8 @@
       <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
-        <v>20</v>
+      <c r="J2" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>21</v>
